--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -1,106 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EffectTag" sheetId="1" r:id="rId1"/>
+    <sheet name="EffectTag" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EffectTag</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>5b023579a94857d9</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>effect_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;Effect.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>length=1..120</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -413,109 +407,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EffectTag</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>5b023579a94857d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>effect_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>effect_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;Effect.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>980504</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>22</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-random-ally</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,32 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>990501</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>direwolf-felling-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>990503</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>coordinates-automaton-grizzly-purge-order</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,32 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1000501</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-applier</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1000502</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>charging-next-action-purge-order</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,6 +652,97 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1010501</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1010501</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>enkindle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1010502</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>spontaneous-combustion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1010503</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1010503</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1010504</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>internal-ai-reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1010505</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>internal-ai-setup</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,6 +743,188 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020501</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>chilling-light</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020502</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sword-formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020502</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020503</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1020503</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>true-weakness-wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1020504</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1020504</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>true-weakness-lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1020505</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020505</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true-weakness-imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1020506</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ordeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1020507</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1020507</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1020508</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>qi-converge-lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020509</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>qi-advance-charge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,84 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1030502</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1030502</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>punishment-damage-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1030503</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>intensifying-cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1030504</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>combat-redeployment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,6 +1003,110 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1040501</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>frigid-waterfall-escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1040502</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>collective-shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1040502</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1040503</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1040503</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>single-trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1040504</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>lock-on</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1040504</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>besiege-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1040505</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>def-down</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,6 +1107,71 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1050501</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1050501</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1050502</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>freezing-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1050502</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1050503</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>internal-ai-reset</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,292 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1060501</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>harrowing-obituary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1060501</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>permanent-damage-growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1060502</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>harrowing-obituary</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1060502</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1060503</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sunset</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1060503</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>nightfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>weakness-protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1060505</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>morbid-dream</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1060505</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1060506</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1060506</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>fixed-hit-bars</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1060510</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1060510</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>captured-formation-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1060511</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1060511</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>captured-formation-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1060512</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1060512</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>captured-formation-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1060513</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1060513</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>captured-formation-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,97 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1070501</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1070501</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>kafka-shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1070502</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>dominated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1070502</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-random-ally</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1070503</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>psychological-suggestion</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1070504</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>cruelty-listener</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1070505</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>griever-damage-growth</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1549,6 +1549,188 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1080501</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>def-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1080501</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>oversaturated-bombardment</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1080502</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>power-amplification</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1080502</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>stackable-damage-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>restrained</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>remove-with-applier</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1080504</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>auxiliary-arm-turn-clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1080505</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>overload-warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1080505</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>controlled-blasting-next-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1080506</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>emergency-support-role</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1080506</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>automaton-beetle</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1080507</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>emergency-support-role</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1080507</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>automaton-hound</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,6 +1731,201 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1095001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>rebound-roar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1095002</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1095003</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1095004</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>rallying-howl</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1095005</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1095006</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>weaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1095007</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>sanction-mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1095007</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1095008</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sanction-mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1095008</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1095009</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>imprisonment</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1095009</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1095010</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>reverberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1095011</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1095012</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>overcombust</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1926,6 +1926,136 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1105001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>chains-of-destruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1105002</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>timed-module</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1105003</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1105004</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>golden-age-binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1105005</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>seeding-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1105006</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>vigor-draining</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1105007</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>inferno-stove</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1105008</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1105009</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sweetness</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1105010</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>rebirth</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2056,6 +2056,175 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1115001</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>channel-state</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1115002</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>bad-roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1115003</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1115004</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>soulglad-party</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1115005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>celebration-fountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1115006</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>alarm-set</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1115007</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>dense-fog</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1115008</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>defense-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1115009</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>candle-flame</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1115010</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>deep-freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1115010</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>speed-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1115011</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1115011</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,201 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1125001</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>performance-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1125002</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>guardian-ban</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1125002</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ability-restriction</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1125003</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>imaginary-armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1125004</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1125005</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1125006</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>entomon-eulogy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1125007</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>prepare-to-fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1125008</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>rebirth</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1125009</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>maddened</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1125009</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ability-replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1125010</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>energy-burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1125010</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1125011</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>aegis</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1125011</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>damage-reduction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2420,6 +2420,396 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1135001</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>faded-rage</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1135001</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>enhanced-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1135002</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>disembodied-shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1135002</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>damage-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1135003</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>mirror-cognition</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1135003</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1135004</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1135005</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>melt</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1135005</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1135006</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>high-temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1135006</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1135007</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>performance-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1135008</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>in-training</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1135008</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1135009</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>covering-support</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1135009</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1135010</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1135011</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>shield-reflect</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1135011</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1135012</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>rallying</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1135012</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1135013</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>storm-cyclone</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1135013</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>life-steal</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1135014</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1135015</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>wind-twisting-crossbow</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1135015</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1135016</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>subduing-prana</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1135016</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1135017</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>prana-snare</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1135017</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>maximum-hp-reduction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2810,6 +2810,318 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1145001</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1145002</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>scared</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1145002</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1145003</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1145003</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1145004</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>cure-you</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1145004</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>damage-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1145005</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>taking-revenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1145005</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>additional-damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1145006</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1145006</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>shared-hit-nullification</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>inspire</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>action-advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>nihility-command</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1145009</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>detonated</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1145009</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>additional-damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1145010</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>overloaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1145011</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>spiral-arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1145011</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1145012</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>entanglement</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1145012</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J203"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3122,6 +3122,71 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1155001</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>spiral-arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1155001</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1155002</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>entanglement</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1155002</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1155003</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/EffectTag.xlsx
+++ b/config/data/EffectTag.xlsx
@@ -1,106 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EffectTag" sheetId="1" r:id="rId1"/>
+    <sheet name="EffectTag" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>EffectTag</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>5b023579a94857d9</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>effect_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;Effect.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>length=1..120</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -119,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -413,109 +407,2784 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J208"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>EffectTag</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>5b023579a94857d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>effect_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>effect_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;Effect.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length=1..120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>980504</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-random-ally</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>990501</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>direwolf-felling-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>990503</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>coordinates-automaton-grizzly-purge-order</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1000501</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-applier</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1000502</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>charging-next-action-purge-order</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1010501</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1010501</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>enkindle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1010502</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>spontaneous-combustion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1010503</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1010503</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1010504</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>internal-ai-reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1010505</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>internal-ai-setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020501</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>chilling-light</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020502</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sword-formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020502</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020503</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1020503</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>true-weakness-wind</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1020504</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1020504</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>true-weakness-lightning</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1020505</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>formation-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020505</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true-weakness-imaginary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1020506</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ordeal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1020507</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1020507</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1020508</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>qi-converge-lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020509</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>qi-advance-charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1030502</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1030502</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>punishment-damage-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1030503</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>intensifying-cold</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1030504</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>combat-redeployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1040501</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>frigid-waterfall-escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1040502</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>collective-shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1040502</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1040503</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1040503</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>single-trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1040504</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>lock-on</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1040504</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>besiege-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1040505</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>def-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1050501</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1050501</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1050502</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>freezing-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1050502</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1050503</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>internal-ai-reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1060501</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>harrowing-obituary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1060501</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>permanent-damage-growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1060502</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>harrowing-obituary</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1060502</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1060503</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sunset</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1060503</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>nightfall</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>weakness-protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C62" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1060504</v>
+      </c>
+      <c r="C63" t="n">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>22</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>remove-on-weakness-break</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1060505</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>morbid-dream</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1060505</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1060506</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1060506</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>fixed-hit-bars</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1060510</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1060510</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>captured-formation-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1060511</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1060511</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>captured-formation-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1060512</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1060512</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>captured-formation-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1060513</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>sombrous-sepulcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1060513</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>captured-formation-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1070501</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1070501</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>kafka-shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1070502</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>dominated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1070502</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>forced-basic-attack-random-ally</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1070503</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>psychological-suggestion</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1070504</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>cruelty-listener</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1070505</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>griever-damage-growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1080501</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>def-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1080501</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>oversaturated-bombardment</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1080502</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>power-amplification</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1080502</v>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>stackable-damage-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>restrained</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1080503</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>remove-with-applier</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1080504</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>auxiliary-arm-turn-clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1080505</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>overload-warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1080505</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>controlled-blasting-next-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1080506</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>emergency-support-role</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1080506</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>automaton-beetle</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1080507</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>emergency-support-role</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1080507</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>automaton-hound</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1095001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>rebound-roar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1095002</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1095003</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1095004</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>rallying-howl</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1095005</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1095006</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>weaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1095007</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>sanction-mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1095007</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1095008</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sanction-mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1095008</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1095009</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>imprisonment</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1095009</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1095010</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>reverberation</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1095011</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1095012</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>overcombust</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1105001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>chains-of-destruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1105002</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>timed-module</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1105003</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1105004</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>golden-age-binding</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1105005</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>seeding-core</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1105006</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>vigor-draining</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1105007</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>inferno-stove</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1105008</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1105009</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sweetness</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1105010</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>rebirth</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1115001</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>channel-state</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1115002</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>bad-roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1115003</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1115004</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>soulglad-party</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1115005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>celebration-fountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1115006</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>alarm-set</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1115007</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>dense-fog</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1115008</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>defense-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1115009</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>candle-flame</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1115010</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>deep-freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1115010</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>speed-down</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1115011</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1115011</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1125001</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>performance-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1125002</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>guardian-ban</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1125002</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ability-restriction</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1125003</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>imaginary-armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1125004</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1125005</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1125006</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>entomon-eulogy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1125007</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>prepare-to-fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1125008</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>rebirth</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1125009</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>maddened</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1125009</v>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ability-replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1125010</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>energy-burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1125010</v>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1125011</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>aegis</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1125011</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>damage-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1135001</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>faded-rage</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1135001</v>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>enhanced-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1135002</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>disembodied-shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1135002</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>damage-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1135003</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>mirror-cognition</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1135003</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1135004</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1135005</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>melt</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1135005</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1135006</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>high-temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1135006</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>toughness-protected</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1135007</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>performance-boost</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1135008</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>in-training</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1135008</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1135009</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>covering-support</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1135009</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1135010</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1135011</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>shield-reflect</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1135011</v>
+      </c>
+      <c r="C168" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1135012</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>rallying</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1135012</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>damage-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1135013</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>storm-cyclone</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1135013</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>life-steal</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1135014</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1135015</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>wind-twisting-crossbow</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1135015</v>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1135016</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>subduing-prana</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1135016</v>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1135017</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>prana-snare</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1135017</v>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>maximum-hp-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1145001</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1145002</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>scared</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1145002</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1145003</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1145003</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>prevents-toughness-reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1145004</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>cure-you</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1145004</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>damage-transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1145005</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>taking-revenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1145005</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>additional-damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1145006</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1145006</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>shared-hit-nullification</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>inspire</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>attack-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1145007</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>action-advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>nihility-command</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1145008</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1145009</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>detonated</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1145009</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>additional-damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1145010</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>overloaded</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1145011</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>spiral-arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1145011</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1145012</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>entanglement</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1145012</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1155001</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>spiral-arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1155001</v>
+      </c>
+      <c r="C205" t="n">
+        <v>2</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>lock-on-target</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1155002</v>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>entanglement</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1155002</v>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>blocks-normal-action</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1155003</v>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>wind-shear</t>
+        </is>
       </c>
     </row>
   </sheetData>
